--- a/events/Crestuma_2009_MAR/Crestuma_2009_MAR_Results.xlsx
+++ b/events/Crestuma_2009_MAR/Crestuma_2009_MAR_Results.xlsx
@@ -4274,11 +4274,6 @@
           <t>01:30:31.100</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t>129697</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -8912,11 +8907,6 @@
           <t>01:32:32.400</t>
         </is>
       </c>
-      <c r="R140" t="inlineStr">
-        <is>
-          <t>73762</t>
-        </is>
-      </c>
       <c r="S140" t="inlineStr">
         <is>
           <t>45212</t>
@@ -11420,11 +11410,6 @@
       <c r="P181" t="inlineStr">
         <is>
           <t>01:20:09.820</t>
-        </is>
-      </c>
-      <c r="S181" t="inlineStr">
-        <is>
-          <t>72616</t>
         </is>
       </c>
     </row>
@@ -19818,7 +19803,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D123"/>
+  <dimension ref="A1:D120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20616,17 +20601,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>129697</t>
+          <t>49433</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Diogo</t>
+          <t>Alvaro</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>FERREIRA</t>
+          <t>FIUZA</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -20638,17 +20623,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>49433</t>
+          <t>58184</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Alvaro</t>
+          <t>Wölke</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FIUZA</t>
+          <t>FLORIAN</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -20660,17 +20645,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>58184</t>
+          <t>63242</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Wölke</t>
+          <t>Manuel</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FLORIAN</t>
+          <t>GARRIDO</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -20682,17 +20667,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>63242</t>
+          <t>46843</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Manuel</t>
+          <t>Carlos</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GARRIDO</t>
+          <t>GARROTE</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -20704,17 +20689,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>46843</t>
+          <t>49642</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Carlos</t>
+          <t>Zsolt</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GARROTE</t>
+          <t>GILANYI</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -20726,83 +20711,83 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>49642</t>
+          <t>36457</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Zsolt</t>
+          <t>Beatriz</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GILANYI</t>
+          <t>GOMES</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>36457</t>
+          <t>50155</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Beatriz</t>
+          <t>Matteo</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GOMES</t>
+          <t>GRAZIANI</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>72616</t>
+          <t>36391</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Adrian</t>
+          <t>Bridgitte</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GONZÁLEZ</t>
+          <t>HARTLEY</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>50155</t>
+          <t>35555</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Matteo</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GRAZIANI</t>
+          <t>HAVEL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -20814,83 +20799,83 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>36391</t>
+          <t>68207</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Bridgitte</t>
+          <t>Nuno</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>HARTLEY</t>
+          <t>HENRIQUES</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>35555</t>
+          <t>68309</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Lorena</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>HAVEL</t>
+          <t>IBAÑEZ</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>68207</t>
+          <t>48496</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nuno</t>
+          <t>Jenny</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>HENRIQUES</t>
+          <t>ILLIDGE</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>68309</t>
+          <t>64839</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Lorena</t>
+          <t>Klein</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>IBAÑEZ</t>
+          <t>JENNIFER</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -20902,39 +20887,39 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>48496</t>
+          <t>49732</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Jenny</t>
+          <t>Tomas</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ILLIDGE</t>
+          <t>JEZEK</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>64839</t>
+          <t>49753</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Klein</t>
+          <t>Michaela</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>JENNIFER</t>
+          <t>JONSSON</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -20946,83 +20931,83 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>49732</t>
+          <t>49637</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tomas</t>
+          <t>Sofie</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>JEZEK</t>
+          <t>JORGENSEN</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>49753</t>
+          <t>42270</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Michaela</t>
+          <t>Mateusz</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>JONSSON</t>
+          <t>KAMINSKI</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>49637</t>
+          <t>45732</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Sofie</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>JORGENSEN</t>
+          <t>KRAJCOVIC</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>42270</t>
+          <t>41547</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Mateusz</t>
+          <t>Tamas</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>KAMINSKI</t>
+          <t>KULIFAI</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -21034,17 +21019,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>45732</t>
+          <t>71560</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Diogo</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>KRAJCOVIC</t>
+          <t>LACERDA</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -21056,17 +21041,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>41547</t>
+          <t>48163</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Tamas</t>
+          <t>Rui</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>KULIFAI</t>
+          <t>LACERDA</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -21078,83 +21063,83 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>71560</t>
+          <t>35325</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Diogo</t>
+          <t>Jamelot</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>LACERDA</t>
+          <t>LEA</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>48163</t>
+          <t>35562</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Rui</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>LACERDA</t>
+          <t>LEHACI</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>35325</t>
+          <t>49267</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Jamelot</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>LEA</t>
+          <t>LEVERETT</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>35562</t>
+          <t>35984</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>Agnes</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>LEHACI</t>
+          <t>LIE</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -21166,17 +21151,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>49267</t>
+          <t>52103</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Johan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>LEVERETT</t>
+          <t>LILJA</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -21188,39 +21173,39 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>35984</t>
+          <t>46833</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Agnes</t>
+          <t>Emilio</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>LIE</t>
+          <t>LLAMEDO</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>52103</t>
+          <t>42771</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Johan</t>
+          <t>Nikica</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>LILJA</t>
+          <t>LOUBEK</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -21232,17 +21217,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>46833</t>
+          <t>42364</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Emilio</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>LLAMEDO</t>
+          <t>LUNACEK</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -21254,39 +21239,39 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>42771</t>
+          <t>46674</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Nikica</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>LOUBEK</t>
+          <t>MACHOVÁ</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>42364</t>
+          <t>58229</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Stuart</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>LUNACEK</t>
+          <t>MACLAREN</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -21298,39 +21283,39 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>46674</t>
+          <t>73693</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Paolo</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MACHOVÁ</t>
+          <t>MARCHETTI</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>58229</t>
+          <t>35291</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Stuart</t>
+          <t>Beugnet</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MACLAREN</t>
+          <t>MATHIEU</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -21342,17 +21327,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>73693</t>
+          <t>49755</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Paolo</t>
+          <t>Ebhardt</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MARCHETTI</t>
+          <t>MATTHIAS</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -21364,39 +21349,39 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>35291</t>
+          <t>52179</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Beugnet</t>
+          <t>Catherine</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MATHIEU</t>
+          <t>MCARTHUR</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>49755</t>
+          <t>48400</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ebhardt</t>
+          <t>Hank</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MATTHIAS</t>
+          <t>McGREGOR</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -21408,39 +21393,39 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>52179</t>
+          <t>42463</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Catherine</t>
+          <t>Chris</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MCARTHUR</t>
+          <t>MEHAK</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>48400</t>
+          <t>49430</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Hank</t>
+          <t>Emilio</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>McGREGOR</t>
+          <t>MERCHAN</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -21452,17 +21437,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>42463</t>
+          <t>44426</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Chris</t>
+          <t>Matej</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MEHAK</t>
+          <t>MICHALEK</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -21474,17 +21459,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>49430</t>
+          <t>47619</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Emilio</t>
+          <t>Rubén</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MERCHAN</t>
+          <t>MILLÁN</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -21496,17 +21481,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>44426</t>
+          <t>35992</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Matej</t>
+          <t>Morten</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>MICHALEK</t>
+          <t>MINDE</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -21518,17 +21503,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>47619</t>
+          <t>49436</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Rubén</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MILLÁN</t>
+          <t>MOSQUERA</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -21540,17 +21525,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>35992</t>
+          <t>47425</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Morten</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MINDE</t>
+          <t>NAGY</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -21562,17 +21547,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>49436</t>
+          <t>42408</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Rodolfo</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MOSQUERA</t>
+          <t>NEVES</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -21584,17 +21569,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>47425</t>
+          <t>42369</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>NAGY</t>
+          <t>ODVARKO</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -21606,17 +21591,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>42408</t>
+          <t>68942</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Rodolfo</t>
+          <t>Radoslaw</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>NEVES</t>
+          <t>OLSZEWSKI</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -21628,17 +21613,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>42369</t>
+          <t>58935</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Pascual</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ODVARKO</t>
+          <t>ORELLANA</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -21650,39 +21635,39 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>68942</t>
+          <t>49441</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Radoslaw</t>
+          <t>Amaya</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>OLSZEWSKI</t>
+          <t>OSABA</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>58935</t>
+          <t>41784</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Pascual</t>
+          <t>Laurens</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ORELLANA</t>
+          <t>PANNECOUCKE</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -21694,39 +21679,39 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>49441</t>
+          <t>68514</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Amaya</t>
+          <t>Wagner</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>OSABA</t>
+          <t>PECORARO</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>41784</t>
+          <t>48494</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Laurens</t>
+          <t>Timothy</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>PANNECOUCKE</t>
+          <t>PENDLE</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -21738,17 +21723,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>68514</t>
+          <t>41787</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Wagner</t>
+          <t>William</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>PECORARO</t>
+          <t>PETERS</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -21760,39 +21745,39 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>48494</t>
+          <t>50157</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Timothy</t>
+          <t>Gaia</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>PENDLE</t>
+          <t>PIAZZA</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>41787</t>
+          <t>35287</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Bayle</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>PETERS</t>
+          <t>PIERRICK</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -21804,39 +21789,39 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>50157</t>
+          <t>49620</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Gaia</t>
+          <t>Orion</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>PIAZZA</t>
+          <t>PILO</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>35287</t>
+          <t>36448</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Bayle</t>
+          <t>Fernando</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>PIERRICK</t>
+          <t>PIMENTA</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -21848,17 +21833,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>49620</t>
+          <t>42336</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Orion</t>
+          <t>Rene</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>PILO</t>
+          <t>POULSEN</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -21870,39 +21855,39 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>36448</t>
+          <t>49622</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Fernando</t>
+          <t>Annemia</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>PIMENTA</t>
+          <t>PRETZMANN</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>42336</t>
+          <t>48161</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Rene</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>POULSEN</t>
+          <t>RAMALHO</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -21914,39 +21899,39 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>49622</t>
+          <t>42535</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Annemia</t>
+          <t>Clin</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>PRETZMANN</t>
+          <t>REMI</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>48161</t>
+          <t>36568</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Nicola</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>RAMALHO</t>
+          <t>RIPAMONTI</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -21958,17 +21943,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>42535</t>
+          <t>54783</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Clin</t>
+          <t>Luca</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>REMI</t>
+          <t>RODEGHER</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -21980,17 +21965,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>36568</t>
+          <t>35293</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Nicola</t>
+          <t>Beugnet</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>RIPAMONTI</t>
+          <t>ROMAIN</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -22002,17 +21987,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>54783</t>
+          <t>46825</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Luca</t>
+          <t>Diego</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>RODEGHER</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -22024,39 +22009,39 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>35293</t>
+          <t>72545</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Beugnet</t>
+          <t>Eukene</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ROMAIN</t>
+          <t>SAEZ</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>46825</t>
+          <t>35981</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Diego</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>SALBU</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -22068,17 +22053,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>72545</t>
+          <t>35321</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Eukene</t>
+          <t>Guyot</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>SAEZ</t>
+          <t>SARAH</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -22090,39 +22075,39 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>35981</t>
+          <t>35561</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Yvonne</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>SALBU</t>
+          <t>SCHURING</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>35321</t>
+          <t>35560</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Guyot</t>
+          <t>Viktoria</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>SARAH</t>
+          <t>SCHWARZ</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -22134,17 +22119,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>35561</t>
+          <t>48740</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Yvonne</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>SCHURING</t>
+          <t>SEGAL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -22156,61 +22141,61 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>35560</t>
+          <t>46397</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Viktoria</t>
+          <t>Eduard</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>SCHWARZ</t>
+          <t>SHEMETYLO</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>48740</t>
+          <t>57969</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Oleksii</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>SEGAL</t>
+          <t>SHPAK</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>46397</t>
+          <t>35980</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Eduard</t>
+          <t>Jo Sondre</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>SHEMETYLO</t>
+          <t>SOLHAUG</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -22222,17 +22207,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>57969</t>
+          <t>97457</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Oleksii</t>
+          <t>Branislav</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>SHPAK</t>
+          <t>SRAMEK</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22244,17 +22229,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>35980</t>
+          <t>42341</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Jo Sondre</t>
+          <t>Emil</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>SOLHAUG</t>
+          <t>STAER</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22266,39 +22251,39 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>97457</t>
+          <t>63631</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Branislav</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SRAMEK</t>
+          <t>SWALLOW</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>42341</t>
+          <t>61252</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Emil</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>STAER</t>
+          <t>TENWOLDE</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22310,61 +22295,61 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>63631</t>
+          <t>61292</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>Malin</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>SWALLOW</t>
+          <t>TITORIC</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>73762</t>
+          <t>49659</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Bence</t>
+          <t>Eniko</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>SZABO</t>
+          <t>VACZAI</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>61252</t>
+          <t>63247</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Carlos</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>TENWOLDE</t>
+          <t>VEGA</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -22376,17 +22361,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>61292</t>
+          <t>36586</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Malin</t>
+          <t>Filippo</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>TITORIC</t>
+          <t>VINCENZI</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -22398,39 +22383,39 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>49659</t>
+          <t>48410</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Eniko</t>
+          <t>Brandon Van Der</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>VACZAI</t>
+          <t>WALT</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>63247</t>
+          <t>41792</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Carlos</t>
+          <t>Joeri</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>VEGA</t>
+          <t>WECKX</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -22442,86 +22427,20 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>36586</t>
+          <t>36310</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Filippo</t>
+          <t>Jost</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>VINCENZI</t>
+          <t>ZAKRAJSEK</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>48410</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Brandon Van Der</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>WALT</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>41792</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Joeri</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>WECKX</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>36310</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Jost</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>ZAKRAJSEK</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
         <is>
           <t>M</t>
         </is>

--- a/events/Crestuma_2009_MAR/Crestuma_2009_MAR_Results.xlsx
+++ b/events/Crestuma_2009_MAR/Crestuma_2009_MAR_Results.xlsx
@@ -13425,6 +13425,11 @@
           <t>01:58:57.720</t>
         </is>
       </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>58775</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -17848,6 +17853,11 @@
           <t>01:58:36.310</t>
         </is>
       </c>
+      <c r="R288" t="inlineStr">
+        <is>
+          <t>58775</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -18404,6 +18414,11 @@
           <t>02:00:57.990</t>
         </is>
       </c>
+      <c r="S297" t="inlineStr">
+        <is>
+          <t>125147</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -18461,6 +18476,11 @@
       <c r="P298" t="inlineStr">
         <is>
           <t>02:01:28.360</t>
+        </is>
+      </c>
+      <c r="R298" t="inlineStr">
+        <is>
+          <t>58936</t>
         </is>
       </c>
     </row>
@@ -19803,7 +19823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D120"/>
+  <dimension ref="A1:D123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22446,6 +22466,72 @@
         </is>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>58775</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Nuno</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>BARROS</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>125147</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Jorge</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>ALONSO</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>58936</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Néstor</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>PINTA</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Crestuma_2009_MAR/Crestuma_2009_MAR_Results.xlsx
+++ b/events/Crestuma_2009_MAR/Crestuma_2009_MAR_Results.xlsx
@@ -4156,6 +4156,11 @@
           <t>01:28:43.750</t>
         </is>
       </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6868,6 +6873,11 @@
           <t>01:58:07.730</t>
         </is>
       </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>49663</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -9409,6 +9419,11 @@
           <t>01:35:43.730</t>
         </is>
       </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>68306</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -14648,6 +14663,11 @@
           <t>02:11:40.220</t>
         </is>
       </c>
+      <c r="R235" t="inlineStr">
+        <is>
+          <t>49744</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -17858,6 +17878,11 @@
           <t>58775</t>
         </is>
       </c>
+      <c r="S288" t="inlineStr">
+        <is>
+          <t>42411</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -18481,6 +18506,11 @@
       <c r="R298" t="inlineStr">
         <is>
           <t>58936</t>
+        </is>
+      </c>
+      <c r="S298" t="inlineStr">
+        <is>
+          <t>58937</t>
         </is>
       </c>
     </row>
@@ -19823,7 +19853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D123"/>
+  <dimension ref="A1:D129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22532,6 +22562,138 @@
         </is>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Dan</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>DRAHOKOUPIL</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>42411</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Helder</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>SILVA</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>49663</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Adrian</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>BOROS</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>49744</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Joep</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>BAKEL VAN</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>58937</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Leonardo Martin</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>MOZZICAFREDO</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>68306</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Vicente</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>CABARRU</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Crestuma_2009_MAR/Crestuma_2009_MAR_Results.xlsx
+++ b/events/Crestuma_2009_MAR/Crestuma_2009_MAR_Results.xlsx
@@ -3136,6 +3136,11 @@
           <t>01:27:26.550</t>
         </is>
       </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>48165</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4279,6 +4284,11 @@
           <t>01:30:31.100</t>
         </is>
       </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>129697</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -11091,6 +11101,11 @@
           <t>01:24:47.050</t>
         </is>
       </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>48165</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -16387,6 +16402,11 @@
       <c r="R264" t="inlineStr">
         <is>
           <t>36457</t>
+        </is>
+      </c>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>36459</t>
         </is>
       </c>
     </row>
@@ -19853,7 +19873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D129"/>
+  <dimension ref="A1:D132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22694,6 +22714,72 @@
         </is>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>36459</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Joana</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>SOUSA</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>48165</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Joana</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>MARINHO SOUSA</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>129697</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Diogo</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>FERREIRA</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Crestuma_2009_MAR/Crestuma_2009_MAR_Results.xlsx
+++ b/events/Crestuma_2009_MAR/Crestuma_2009_MAR_Results.xlsx
@@ -4284,11 +4284,6 @@
           <t>01:30:31.100</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t>129697</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -19873,7 +19868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D132"/>
+  <dimension ref="A1:D131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22758,28 +22753,6 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>129697</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Diogo</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>FERREIRA</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Crestuma_2009_MAR/Crestuma_2009_MAR_Results.xlsx
+++ b/events/Crestuma_2009_MAR/Crestuma_2009_MAR_Results.xlsx
@@ -4519,6 +4519,11 @@
       <c r="L67" t="n">
         <v>68</v>
       </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>47426</t>
+        </is>
+      </c>
       <c r="X67" t="inlineStr">
         <is>
           <t>DNF</t>
@@ -11882,6 +11887,11 @@
       </c>
       <c r="L189" t="n">
         <v>190</v>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>47426</t>
+        </is>
       </c>
       <c r="X189" t="inlineStr">
         <is>
@@ -19868,7 +19878,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D131"/>
+  <dimension ref="A1:D132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22753,6 +22763,28 @@
         </is>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>47426</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Henrik</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>VASBAYAI</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
